--- a/downloads/plantilla_costo_punto_adherencia.xlsx
+++ b/downloads/plantilla_costo_punto_adherencia.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Ejercicio de clase · incentivo (ilustrativo)</t>
+          <t>Ejercicio ilustrativo · incentivo</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -983,12 +983,12 @@
     <row r="3" ht="75" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Ejercicio de clase</t>
+          <t>Ejercicio ilustrativo</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Datos ficticios con fines didácticos: incentivo de 240.000 pesos por paciente durante seis meses; adherencia del 50 % al 62 %, y del 52 % tras retirar el incentivo.</t>
+          <t>Datos ficticios: incentivo de 240.000 pesos por paciente durante seis meses; adherencia del 50 % al 62 %, y del 52 % tras retirar el incentivo.</t>
         </is>
       </c>
     </row>
